--- a/data_search/Other_EHI_studies.xlsx
+++ b/data_search/Other_EHI_studies.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Desktop\EHI_laterality\data_search\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1D3284D-CC3A-4F09-AFF0-393BBA65B4DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CCEEBC6-2248-4DBC-8681-8B6F3B55B973}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -354,7 +354,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -364,6 +364,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -396,8 +399,8 @@
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>309064</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>181545</xdr:rowOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>116</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -836,7 +839,7 @@
       <c r="D4" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="1" t="s">
         <v>24</v>
       </c>
     </row>
@@ -904,7 +907,7 @@
       <c r="D8" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="5" t="s">
         <v>47</v>
       </c>
     </row>
@@ -921,7 +924,7 @@
       <c r="D9" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="5" t="s">
         <v>54</v>
       </c>
     </row>
@@ -939,9 +942,12 @@
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1" tooltip="Persistent link using digital object identifier" xr:uid="{ED9D1B3F-BDEB-4A73-8EA5-FD330C7D9646}"/>
     <hyperlink ref="E3" r:id="rId2" tooltip="Persistent link using digital object identifier" xr:uid="{3000918C-D377-4F7B-85B3-84D283F4E472}"/>
+    <hyperlink ref="E9" r:id="rId3" xr:uid="{A51779EE-167B-4D59-B1E2-714582052BEF}"/>
+    <hyperlink ref="E4" r:id="rId4" xr:uid="{2C76EF9B-5DEE-4B00-BA68-C59F97AFFF59}"/>
+    <hyperlink ref="E8" r:id="rId5" xr:uid="{7964CAB7-B8A2-4369-AEC9-A2670FAA83CB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId3"/>
+  <drawing r:id="rId6"/>
 </worksheet>
 </file>
 
@@ -966,7 +972,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" tooltip="Persistent link using digital object identifier" xr:uid="{416C6098-32A6-46FE-9250-589821295065}"/>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{416C6098-32A6-46FE-9250-589821295065}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId2"/>
